--- a/data/trans_orig/P16A11-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P16A11-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23892</t>
+          <t>24640</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43863</t>
+          <t>45246</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27893</t>
+          <t>28087</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49802</t>
+          <t>50697</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>58062</t>
+          <t>58094</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>89675</t>
+          <t>87558</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,4%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>229147</t>
+          <t>227764</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>249118</t>
+          <t>248370</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>211036</t>
+          <t>210141</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>232945</t>
+          <t>232751</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>444173</t>
+          <t>446290</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>475786</t>
+          <t>475754</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41272</t>
+          <t>42044</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>69228</t>
+          <t>69349</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>73558</t>
+          <t>74238</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>106749</t>
+          <t>108751</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>122994</t>
+          <t>119971</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>166783</t>
+          <t>167360</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,79%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>423847</t>
+          <t>423726</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>451803</t>
+          <t>451031</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>397200</t>
+          <t>395198</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>430391</t>
+          <t>429711</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>830241</t>
+          <t>829664</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>874030</t>
+          <t>877053</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,97%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33048</t>
+          <t>31820</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>56055</t>
+          <t>55918</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>52364</t>
+          <t>52631</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>82636</t>
+          <t>81118</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>91470</t>
+          <t>92364</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>128608</t>
+          <t>128796</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,69%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>262791</t>
+          <t>262928</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>285798</t>
+          <t>287026</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>252776</t>
+          <t>254294</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>283048</t>
+          <t>282781</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>525650</t>
+          <t>525462</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>562788</t>
+          <t>561894</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>85,88%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35880</t>
+          <t>36063</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>61208</t>
+          <t>60414</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53398</t>
+          <t>54375</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>81676</t>
+          <t>83236</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>96639</t>
+          <t>97207</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>134437</t>
+          <t>133742</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,32%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>297463</t>
+          <t>298257</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>322791</t>
+          <t>322608</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>289780</t>
+          <t>288220</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>318058</t>
+          <t>317081</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>595690</t>
+          <t>596385</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>633488</t>
+          <t>632920</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,69%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11471</t>
+          <t>10786</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27120</t>
+          <t>26771</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16384</t>
+          <t>16060</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>36921</t>
+          <t>35902</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32262</t>
+          <t>31746</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>57274</t>
+          <t>56571</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,77%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>176188</t>
+          <t>176537</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>191837</t>
+          <t>192522</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>170747</t>
+          <t>171766</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>191284</t>
+          <t>191608</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>353702</t>
+          <t>354405</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>378714</t>
+          <t>379230</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,28%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>31083</t>
+          <t>31177</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>54873</t>
+          <t>53687</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>41393</t>
+          <t>41192</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>68999</t>
+          <t>65681</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>80251</t>
+          <t>77277</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>114658</t>
+          <t>113899</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,75%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>215938</t>
+          <t>217124</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>239728</t>
+          <t>239634</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>209145</t>
+          <t>212463</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>236751</t>
+          <t>236952</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>434297</t>
+          <t>435056</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>468704</t>
+          <t>471678</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,92%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>71297</t>
+          <t>73635</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>107892</t>
+          <t>108861</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>100080</t>
+          <t>98386</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>136919</t>
+          <t>139451</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>183703</t>
+          <t>180169</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>235919</t>
+          <t>232259</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,53%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>507135</t>
+          <t>506166</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>543730</t>
+          <t>541392</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>501300</t>
+          <t>498768</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>538139</t>
+          <t>539833</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1017327</t>
+          <t>1020987</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1069543</t>
+          <t>1073077</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,62%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>70891</t>
+          <t>70989</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>104585</t>
+          <t>105813</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>84387</t>
+          <t>85676</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>123653</t>
+          <t>127165</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>164976</t>
+          <t>164627</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>217924</t>
+          <t>218594</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,32%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>638192</t>
+          <t>636964</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>671886</t>
+          <t>671788</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>659858</t>
+          <t>656346</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>699124</t>
+          <t>697835</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1308364</t>
+          <t>1307694</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1361312</t>
+          <t>1361661</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,21%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>379776</t>
+          <t>379184</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>455223</t>
+          <t>449429</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>520780</t>
+          <t>525033</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>611006</t>
+          <t>608714</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>920899</t>
+          <t>922669</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1037997</t>
+          <t>1040186</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,63%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2820302</t>
+          <t>2826096</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2895749</t>
+          <t>2896341</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2768191</t>
+          <t>2770483</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2858417</t>
+          <t>2854164</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5616725</t>
+          <t>5614536</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5733823</t>
+          <t>5732053</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,14%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas en 2012 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24546</t>
+          <t>23434</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48627</t>
+          <t>46934</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32738</t>
+          <t>32743</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>58280</t>
+          <t>58104</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>62407</t>
+          <t>63835</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>98104</t>
+          <t>98250</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,08%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>244382</t>
+          <t>246075</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>268463</t>
+          <t>269575</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>224043</t>
+          <t>224219</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>249585</t>
+          <t>249580</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>477229</t>
+          <t>477083</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>512926</t>
+          <t>511498</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>82,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>88,9%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>62914</t>
+          <t>65073</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>98400</t>
+          <t>99898</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>88994</t>
+          <t>90129</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>126953</t>
+          <t>128847</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>162829</t>
+          <t>161578</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>214775</t>
+          <t>209812</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,4%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>407127</t>
+          <t>405629</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>442613</t>
+          <t>440454</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>80,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>395778</t>
+          <t>393884</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>433737</t>
+          <t>432602</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>813483</t>
+          <t>818446</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>865429</t>
+          <t>866680</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>84,29%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45710</t>
+          <t>45091</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>76016</t>
+          <t>74277</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>62695</t>
+          <t>63935</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>93060</t>
+          <t>94764</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>117205</t>
+          <t>117805</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>159711</t>
+          <t>159745</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>247100</t>
+          <t>248839</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>277406</t>
+          <t>278025</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>247960</t>
+          <t>246256</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>278325</t>
+          <t>277085</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>504425</t>
+          <t>504391</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>546931</t>
+          <t>546331</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,26%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>54475</t>
+          <t>53772</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>85896</t>
+          <t>84511</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>79433</t>
+          <t>80677</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>114648</t>
+          <t>115099</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>142678</t>
+          <t>140622</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>189114</t>
+          <t>187884</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,66%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>288086</t>
+          <t>289471</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>319507</t>
+          <t>320210</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>77,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>273326</t>
+          <t>272875</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>308541</t>
+          <t>307297</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>70,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>572842</t>
+          <t>574072</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>619278</t>
+          <t>621334</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>81,54%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23083</t>
+          <t>22956</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>44585</t>
+          <t>45566</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>44602</t>
+          <t>45442</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>71936</t>
+          <t>72038</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>74108</t>
+          <t>73730</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>108315</t>
+          <t>110764</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,63%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>168033</t>
+          <t>167052</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>189535</t>
+          <t>189662</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>147655</t>
+          <t>147553</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>174989</t>
+          <t>174149</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>67,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>323894</t>
+          <t>321445</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>358101</t>
+          <t>358479</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>82,94%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>50174</t>
+          <t>48450</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>78325</t>
+          <t>77659</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>50914</t>
+          <t>50027</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>78713</t>
+          <t>77703</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>107379</t>
+          <t>108072</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>146597</t>
+          <t>146865</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,55%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>195656</t>
+          <t>196322</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>223807</t>
+          <t>225531</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>200427</t>
+          <t>201437</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>228226</t>
+          <t>229113</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>406524</t>
+          <t>406256</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>445742</t>
+          <t>445049</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>80,46%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>101609</t>
+          <t>103299</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>140512</t>
+          <t>143344</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>134823</t>
+          <t>138685</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>181951</t>
+          <t>181731</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>247534</t>
+          <t>252315</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>306763</t>
+          <t>313436</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>23,1%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>522276</t>
+          <t>519444</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>561179</t>
+          <t>559489</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,37%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>511902</t>
+          <t>512122</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>559030</t>
+          <t>555168</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1049878</t>
+          <t>1043205</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1109107</t>
+          <t>1104326</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>81,4%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>91012</t>
+          <t>91307</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>131814</t>
+          <t>132187</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>112445</t>
+          <t>115126</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>156892</t>
+          <t>158760</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>217498</t>
+          <t>217640</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>275684</t>
+          <t>274793</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,2%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>645158</t>
+          <t>644785</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>685960</t>
+          <t>685665</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>663503</t>
+          <t>661635</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>707950</t>
+          <t>705269</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1321683</t>
+          <t>1322574</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1379869</t>
+          <t>1379727</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>521960</t>
+          <t>527150</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>617425</t>
+          <t>617562</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>695928</t>
+          <t>693845</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>791566</t>
+          <t>796944</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1243721</t>
+          <t>1249357</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1377777</t>
+          <t>1382581</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,84%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2804569</t>
+          <t>2804432</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2900034</t>
+          <t>2894844</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2755462</t>
+          <t>2750084</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2851100</t>
+          <t>2853183</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5591244</t>
+          <t>5586440</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5725300</t>
+          <t>5719664</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>82,07%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20196</t>
+          <t>20858</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42466</t>
+          <t>42119</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26179</t>
+          <t>26079</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50092</t>
+          <t>48821</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>51194</t>
+          <t>51782</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>82013</t>
+          <t>84671</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,54%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>251295</t>
+          <t>251642</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>273565</t>
+          <t>272903</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>238611</t>
+          <t>239882</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>262524</t>
+          <t>262624</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>500451</t>
+          <t>497793</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>531270</t>
+          <t>530682</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,11%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64093</t>
+          <t>65035</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>98849</t>
+          <t>98901</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>98657</t>
+          <t>99053</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>139749</t>
+          <t>138894</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>172683</t>
+          <t>176022</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>225841</t>
+          <t>227801</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,21%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>403726</t>
+          <t>403674</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>438482</t>
+          <t>437540</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>383335</t>
+          <t>384190</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>424427</t>
+          <t>424031</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>799818</t>
+          <t>797858</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>852976</t>
+          <t>849637</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>82,84%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38721</t>
+          <t>36438</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62988</t>
+          <t>61039</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37365</t>
+          <t>39659</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>67069</t>
+          <t>66864</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>84270</t>
+          <t>83655</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>120636</t>
+          <t>120645</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>255577</t>
+          <t>257526</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>279844</t>
+          <t>282127</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>269240</t>
+          <t>269445</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>298944</t>
+          <t>296650</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>534238</t>
+          <t>534229</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>570604</t>
+          <t>571219</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,23%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49289</t>
+          <t>49685</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>77284</t>
+          <t>78029</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>65522</t>
+          <t>66591</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>100650</t>
+          <t>101983</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>124018</t>
+          <t>122687</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>170750</t>
+          <t>169634</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,4%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>292680</t>
+          <t>291935</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>320675</t>
+          <t>320279</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>78,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>286633</t>
+          <t>285300</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>321761</t>
+          <t>320692</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>586497</t>
+          <t>587613</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>633229</t>
+          <t>634560</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>83,8%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15010</t>
+          <t>15355</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33597</t>
+          <t>34723</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31862</t>
+          <t>32138</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>56053</t>
+          <t>55945</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>50701</t>
+          <t>51997</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>80907</t>
+          <t>80490</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,73%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>177624</t>
+          <t>176498</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>196211</t>
+          <t>195866</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>162534</t>
+          <t>162642</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>186725</t>
+          <t>186449</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>74,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>348901</t>
+          <t>349318</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>379107</t>
+          <t>377811</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>87,9%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25467</t>
+          <t>26382</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>49083</t>
+          <t>47741</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34613</t>
+          <t>34079</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>59598</t>
+          <t>58599</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>65820</t>
+          <t>65535</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>99212</t>
+          <t>97936</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,26%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>214040</t>
+          <t>215382</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>237656</t>
+          <t>236741</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>213517</t>
+          <t>214516</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>238502</t>
+          <t>239036</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>437026</t>
+          <t>438302</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>470418</t>
+          <t>470703</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,78%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>79371</t>
+          <t>79019</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>116065</t>
+          <t>116718</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>80121</t>
+          <t>80361</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>116778</t>
+          <t>120006</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>170076</t>
+          <t>169055</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>225255</t>
+          <t>224127</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,63%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>540493</t>
+          <t>539840</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>577187</t>
+          <t>577539</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>574516</t>
+          <t>571288</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>611173</t>
+          <t>610933</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1122597</t>
+          <t>1123725</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1177776</t>
+          <t>1178797</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,46%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>106790</t>
+          <t>107778</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>147097</t>
+          <t>147670</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>130564</t>
+          <t>130793</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>179597</t>
+          <t>179117</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>248593</t>
+          <t>249916</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>312185</t>
+          <t>314210</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,58%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>631486</t>
+          <t>630913</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>671793</t>
+          <t>670805</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>646570</t>
+          <t>647050</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>695603</t>
+          <t>695374</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>78,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1292565</t>
+          <t>1290540</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1356157</t>
+          <t>1354834</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,43%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>464438</t>
+          <t>464682</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>546579</t>
+          <t>550516</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>582339</t>
+          <t>582402</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>677238</t>
+          <t>675898</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1072519</t>
+          <t>1071688</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1202296</t>
+          <t>1196193</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,24%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2847771</t>
+          <t>2843834</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2929912</t>
+          <t>2929668</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2867304</t>
+          <t>2868644</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2962203</t>
+          <t>2962140</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5736596</t>
+          <t>5742699</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5866373</t>
+          <t>5867204</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,56%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas en 2023 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>47516</t>
+          <t>47911</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>75286</t>
+          <t>75835</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44396</t>
+          <t>43938</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>63730</t>
+          <t>63929</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>98207</t>
+          <t>98452</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>131493</t>
+          <t>130547</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,72%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>236157</t>
+          <t>235608</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>263927</t>
+          <t>263532</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>225905</t>
+          <t>225706</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>245239</t>
+          <t>245697</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>77,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>469584</t>
+          <t>470530</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>502870</t>
+          <t>502625</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>78,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,62%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>62046</t>
+          <t>63007</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>98634</t>
+          <t>96811</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>65002</t>
+          <t>64161</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>91863</t>
+          <t>90727</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>134970</t>
+          <t>134113</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>176725</t>
+          <t>177230</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,2%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>417875</t>
+          <t>419698</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>454463</t>
+          <t>453502</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>421862</t>
+          <t>422998</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>448723</t>
+          <t>449564</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>853509</t>
+          <t>853004</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>895264</t>
+          <t>896121</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>86,98%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>56736</t>
+          <t>57025</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>82446</t>
+          <t>81463</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>71665</t>
+          <t>71935</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>97294</t>
+          <t>97417</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>136456</t>
+          <t>134185</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>174070</t>
+          <t>170901</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>25,69%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>233604</t>
+          <t>234587</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>259314</t>
+          <t>259025</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>251834</t>
+          <t>251711</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>277463</t>
+          <t>277193</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>72,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>491108</t>
+          <t>494277</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>528722</t>
+          <t>530993</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>74,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,83%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48329</t>
+          <t>49783</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76892</t>
+          <t>78782</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49216</t>
+          <t>51490</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>106630</t>
+          <t>108234</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>106867</t>
+          <t>104351</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>172408</t>
+          <t>172297</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,86%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>235665</t>
+          <t>233775</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>264228</t>
+          <t>262774</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>74,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>369088</t>
+          <t>367484</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>426502</t>
+          <t>424228</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>615866</t>
+          <t>615977</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>681407</t>
+          <t>683923</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>86,76%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27092</t>
+          <t>26688</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42453</t>
+          <t>43513</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>48179</t>
+          <t>47063</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>63502</t>
+          <t>64378</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,47 +12124,47 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
+          <t>22,56%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>30,85%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>89468</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>78454</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>101160</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
           <t>23,09%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>30,43%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>89468</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>78766</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>101609</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>23,09%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,11%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>136289</t>
+          <t>135229</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>151650</t>
+          <t>152054</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>75,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>145154</t>
+          <t>144278</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>160477</t>
+          <t>161593</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,47 +12237,47 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
+          <t>77,44%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>558</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>297930</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>286238</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>308944</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
           <t>76,91%</t>
         </is>
       </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>558</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>297930</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>285789</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>308632</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>76,91%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>79,75%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>62523</t>
+          <t>62377</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>86698</t>
+          <t>86420</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>51620</t>
+          <t>51598</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>70421</t>
+          <t>70633</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>119460</t>
+          <t>119026</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>149624</t>
+          <t>148919</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,27%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>182938</t>
+          <t>183216</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>207113</t>
+          <t>207259</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>76,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>186635</t>
+          <t>186423</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>205436</t>
+          <t>205458</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>377068</t>
+          <t>377773</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>407232</t>
+          <t>407666</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>71,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,32%</t>
+          <t>77,4%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>91645</t>
+          <t>91634</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>129491</t>
+          <t>129153</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12780,7 +12780,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>161194</t>
+          <t>157596</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>557995</t>
+          <t>587135</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>266907</t>
+          <t>264543</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>854083</t>
+          <t>801865</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>54,42%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>494788</t>
+          <t>495126</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>532634</t>
+          <t>532645</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>291270</t>
+          <t>262130</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>688071</t>
+          <t>691669</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>619461</t>
+          <t>671679</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1206637</t>
+          <t>1209001</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>82,05%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>55473</t>
+          <t>56136</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>179654</t>
+          <t>177018</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>141768</t>
+          <t>142612</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>179168</t>
+          <t>179945</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>174550</t>
+          <t>169733</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>343384</t>
+          <t>343874</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,92%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>749066</t>
+          <t>751702</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>873247</t>
+          <t>872584</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>535683</t>
+          <t>534906</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>573083</t>
+          <t>572239</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>74,83%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1300188</t>
+          <t>1299698</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1469022</t>
+          <t>1473839</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,67%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>472651</t>
+          <t>468711</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>678362</t>
+          <t>672069</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>724417</t>
+          <t>721775</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1439981</t>
+          <t>1386413</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1316310</t>
+          <t>1305539</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2143246</t>
+          <t>2162816</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,39%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2779575</t>
+          <t>2785868</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2985286</t>
+          <t>2989226</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2218052</t>
+          <t>2271620</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2933616</t>
+          <t>2936258</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4972723</t>
+          <t>4953153</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5799659</t>
+          <t>5810430</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>81,65%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A11-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P16A11-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24640</t>
+          <t>23793</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45246</t>
+          <t>44841</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28087</t>
+          <t>28188</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50697</t>
+          <t>50424</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>58094</t>
+          <t>56962</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>87558</t>
+          <t>86657</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,23%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>227764</t>
+          <t>228169</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>248370</t>
+          <t>249217</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>210141</t>
+          <t>210414</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>232751</t>
+          <t>232650</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>446290</t>
+          <t>447191</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>475754</t>
+          <t>476886</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,33%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42044</t>
+          <t>40294</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>69349</t>
+          <t>69178</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>74238</t>
+          <t>74575</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>108751</t>
+          <t>107577</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>119971</t>
+          <t>122465</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>167360</t>
+          <t>167710</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,82%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>423726</t>
+          <t>423897</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>451031</t>
+          <t>452781</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>395198</t>
+          <t>396372</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>429711</t>
+          <t>429374</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>829664</t>
+          <t>829314</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>877053</t>
+          <t>874559</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>87,72%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31820</t>
+          <t>32460</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55918</t>
+          <t>57244</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>52631</t>
+          <t>50304</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>81118</t>
+          <t>80002</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>92364</t>
+          <t>91642</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>128796</t>
+          <t>128819</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>262928</t>
+          <t>261602</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>287026</t>
+          <t>286386</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>254294</t>
+          <t>255410</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>282781</t>
+          <t>285108</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>76,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>525462</t>
+          <t>525439</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>561894</t>
+          <t>562616</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>85,99%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36063</t>
+          <t>35992</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60414</t>
+          <t>59831</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>54375</t>
+          <t>53936</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>83236</t>
+          <t>83178</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>97207</t>
+          <t>96872</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>133742</t>
+          <t>133736</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>298257</t>
+          <t>298840</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>322608</t>
+          <t>322679</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>288220</t>
+          <t>288278</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>317081</t>
+          <t>317520</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>596385</t>
+          <t>596391</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>632920</t>
+          <t>633255</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,73%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10786</t>
+          <t>11100</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26771</t>
+          <t>26922</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16060</t>
+          <t>16418</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35902</t>
+          <t>35452</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31746</t>
+          <t>30801</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56571</t>
+          <t>56004</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,63%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>176537</t>
+          <t>176386</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>192522</t>
+          <t>192208</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>171766</t>
+          <t>172216</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>191608</t>
+          <t>191250</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>354405</t>
+          <t>354972</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>379230</t>
+          <t>380175</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,51%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>31177</t>
+          <t>31352</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>53687</t>
+          <t>55616</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>41192</t>
+          <t>40696</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>65681</t>
+          <t>67435</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>77277</t>
+          <t>77082</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>113899</t>
+          <t>113827</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,74%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>217124</t>
+          <t>215195</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>239634</t>
+          <t>239459</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>212463</t>
+          <t>210709</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>236952</t>
+          <t>237448</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>435056</t>
+          <t>435128</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>471678</t>
+          <t>471873</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,96%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>73635</t>
+          <t>73672</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>108861</t>
+          <t>107545</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>98386</t>
+          <t>99175</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>139451</t>
+          <t>139191</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>180169</t>
+          <t>183125</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>232259</t>
+          <t>235190</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,77%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>506166</t>
+          <t>507482</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>541392</t>
+          <t>541355</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>498768</t>
+          <t>499028</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>539833</t>
+          <t>539044</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1020987</t>
+          <t>1018056</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1073077</t>
+          <t>1070121</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,39%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>70989</t>
+          <t>70940</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>105813</t>
+          <t>104692</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>85676</t>
+          <t>85170</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>127165</t>
+          <t>124549</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>164627</t>
+          <t>168036</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>218594</t>
+          <t>218589</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>636964</t>
+          <t>638085</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>671788</t>
+          <t>671837</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>656346</t>
+          <t>658962</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>697835</t>
+          <t>698341</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1307694</t>
+          <t>1307699</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1361661</t>
+          <t>1358252</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>88,99%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>379184</t>
+          <t>380247</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>449429</t>
+          <t>452546</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>525033</t>
+          <t>524789</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>608714</t>
+          <t>611644</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>922669</t>
+          <t>915783</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1040186</t>
+          <t>1028937</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,46%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2826096</t>
+          <t>2822979</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2896341</t>
+          <t>2895278</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2770483</t>
+          <t>2767553</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2854164</t>
+          <t>2854408</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5614536</t>
+          <t>5625785</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5732053</t>
+          <t>5738939</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,24%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23434</t>
+          <t>24287</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46934</t>
+          <t>47246</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32743</t>
+          <t>33729</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>58104</t>
+          <t>58814</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>63835</t>
+          <t>63064</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>98250</t>
+          <t>98050</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,04%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>246075</t>
+          <t>245763</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>269575</t>
+          <t>268722</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>224219</t>
+          <t>223509</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>249580</t>
+          <t>248594</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>477083</t>
+          <t>477283</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>511498</t>
+          <t>512269</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>89,04%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>65073</t>
+          <t>63953</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>99898</t>
+          <t>100069</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>90129</t>
+          <t>88964</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>128847</t>
+          <t>126393</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>161578</t>
+          <t>164038</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>209812</t>
+          <t>214843</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,89%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>405629</t>
+          <t>405458</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>440454</t>
+          <t>441574</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>393884</t>
+          <t>396338</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>432602</t>
+          <t>433767</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>818446</t>
+          <t>813415</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>866680</t>
+          <t>864220</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>84,05%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45091</t>
+          <t>45786</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>74277</t>
+          <t>75096</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>63935</t>
+          <t>63132</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>94764</t>
+          <t>95308</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>117805</t>
+          <t>117839</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>159745</t>
+          <t>159992</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,09%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>248839</t>
+          <t>248020</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>278025</t>
+          <t>277330</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>246256</t>
+          <t>245712</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>277085</t>
+          <t>277888</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>504391</t>
+          <t>504144</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>546331</t>
+          <t>546297</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53772</t>
+          <t>53087</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84511</t>
+          <t>84723</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>80677</t>
+          <t>80762</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>115099</t>
+          <t>114009</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>140622</t>
+          <t>141494</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>187884</t>
+          <t>187998</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,67%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>289471</t>
+          <t>289259</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>320210</t>
+          <t>320895</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>272875</t>
+          <t>273965</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>307297</t>
+          <t>307212</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,33%</t>
+          <t>70,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>574072</t>
+          <t>573958</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>621334</t>
+          <t>620462</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,43%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22956</t>
+          <t>23194</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45566</t>
+          <t>44772</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>45442</t>
+          <t>46290</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>72038</t>
+          <t>70917</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>73730</t>
+          <t>73390</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>110764</t>
+          <t>107935</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>24,97%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>167052</t>
+          <t>167846</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>189662</t>
+          <t>189424</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>147553</t>
+          <t>148674</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>174149</t>
+          <t>173301</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>78,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>321445</t>
+          <t>324274</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>358479</t>
+          <t>358819</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>83,02%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>48450</t>
+          <t>49120</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>77659</t>
+          <t>78354</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>50027</t>
+          <t>51255</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>77703</t>
+          <t>79439</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>108072</t>
+          <t>107432</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>146865</t>
+          <t>146829</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>196322</t>
+          <t>195627</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>225531</t>
+          <t>224861</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>201437</t>
+          <t>199701</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>229113</t>
+          <t>227885</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>406256</t>
+          <t>406292</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>445049</t>
+          <t>445689</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,58%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>103299</t>
+          <t>100173</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>143344</t>
+          <t>145171</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>138685</t>
+          <t>135130</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>181731</t>
+          <t>182545</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>252315</t>
+          <t>248664</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>313436</t>
+          <t>310174</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>22,86%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>519444</t>
+          <t>517617</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>559489</t>
+          <t>562615</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>512122</t>
+          <t>511308</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>555168</t>
+          <t>558723</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1043205</t>
+          <t>1046467</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1104326</t>
+          <t>1107977</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,67%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>91307</t>
+          <t>90549</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>132187</t>
+          <t>131059</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>115126</t>
+          <t>115472</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>158760</t>
+          <t>160768</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>217640</t>
+          <t>216681</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>274793</t>
+          <t>276184</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,29%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>644785</t>
+          <t>645913</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>685665</t>
+          <t>686423</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>661635</t>
+          <t>659627</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>705269</t>
+          <t>704923</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1322574</t>
+          <t>1321183</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1379727</t>
+          <t>1380686</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,44%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>527150</t>
+          <t>526209</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>617562</t>
+          <t>616452</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>693845</t>
+          <t>690133</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>796944</t>
+          <t>794399</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1249357</t>
+          <t>1249622</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1382581</t>
+          <t>1381315</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,82%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2804432</t>
+          <t>2805542</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2894844</t>
+          <t>2895785</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2750084</t>
+          <t>2752629</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2853183</t>
+          <t>2856895</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5586440</t>
+          <t>5587706</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5719664</t>
+          <t>5719399</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20858</t>
+          <t>20634</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42119</t>
+          <t>41887</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26079</t>
+          <t>25572</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48821</t>
+          <t>49170</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>51782</t>
+          <t>51343</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84671</t>
+          <t>83450</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,33%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>251642</t>
+          <t>251874</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>272903</t>
+          <t>273127</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>239882</t>
+          <t>239533</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>262624</t>
+          <t>263131</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>497793</t>
+          <t>499014</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>530682</t>
+          <t>531121</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,19%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>65035</t>
+          <t>64092</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>98901</t>
+          <t>98235</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>99053</t>
+          <t>99997</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>138894</t>
+          <t>139673</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>176022</t>
+          <t>174968</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>227801</t>
+          <t>225326</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>21,97%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>403674</t>
+          <t>404340</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>437540</t>
+          <t>438483</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>384190</t>
+          <t>383411</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>424031</t>
+          <t>423087</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>797858</t>
+          <t>800333</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>849637</t>
+          <t>850691</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>82,94%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36438</t>
+          <t>37371</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61039</t>
+          <t>62183</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39659</t>
+          <t>40239</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>66864</t>
+          <t>67411</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>83655</t>
+          <t>84463</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>120645</t>
+          <t>119698</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,28%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>257526</t>
+          <t>256382</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>282127</t>
+          <t>281194</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>269445</t>
+          <t>268898</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>296650</t>
+          <t>296070</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>534229</t>
+          <t>535176</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>571219</t>
+          <t>570411</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,1%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49685</t>
+          <t>48920</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>78029</t>
+          <t>77672</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>66591</t>
+          <t>66107</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>101983</t>
+          <t>102846</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>122687</t>
+          <t>125037</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>169634</t>
+          <t>169229</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,35%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>291935</t>
+          <t>292292</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>320279</t>
+          <t>321044</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>285300</t>
+          <t>284437</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>320692</t>
+          <t>321176</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>587613</t>
+          <t>588018</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>634560</t>
+          <t>632210</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>83,49%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15355</t>
+          <t>14975</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34723</t>
+          <t>34068</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32138</t>
+          <t>31420</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55945</t>
+          <t>54880</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>51997</t>
+          <t>51558</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>80490</t>
+          <t>80478</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,72%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>176498</t>
+          <t>177153</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>195866</t>
+          <t>196246</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>162642</t>
+          <t>163707</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>186449</t>
+          <t>187167</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>349318</t>
+          <t>349330</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>377811</t>
+          <t>378250</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>88,0%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26382</t>
+          <t>26924</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>47741</t>
+          <t>47639</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34079</t>
+          <t>33768</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>58599</t>
+          <t>60185</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>65535</t>
+          <t>65546</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>97936</t>
+          <t>98945</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,45%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>215382</t>
+          <t>215484</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>236741</t>
+          <t>236199</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>214516</t>
+          <t>212930</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>239036</t>
+          <t>239347</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>438302</t>
+          <t>437293</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>470703</t>
+          <t>470692</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>79019</t>
+          <t>79892</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>116718</t>
+          <t>116081</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>80361</t>
+          <t>80701</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>120006</t>
+          <t>118318</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>169055</t>
+          <t>170718</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>224127</t>
+          <t>222790</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,53%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>539840</t>
+          <t>540477</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>577539</t>
+          <t>576666</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>571288</t>
+          <t>572976</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>610933</t>
+          <t>610593</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1123725</t>
+          <t>1125062</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1178797</t>
+          <t>1177134</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,33%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>107778</t>
+          <t>106067</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>147670</t>
+          <t>148760</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>130793</t>
+          <t>129152</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>179117</t>
+          <t>178191</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>249916</t>
+          <t>246503</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>314210</t>
+          <t>312594</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,48%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>630913</t>
+          <t>629823</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>670805</t>
+          <t>672516</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>647050</t>
+          <t>647976</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>695374</t>
+          <t>697015</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>78,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1290540</t>
+          <t>1292156</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1354834</t>
+          <t>1358247</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,64%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>464682</t>
+          <t>460657</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>550516</t>
+          <t>542765</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>582402</t>
+          <t>581873</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>675898</t>
+          <t>681888</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1071688</t>
+          <t>1072991</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1196193</t>
+          <t>1201570</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,32%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2843834</t>
+          <t>2851585</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2929668</t>
+          <t>2933693</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2868644</t>
+          <t>2862654</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2962140</t>
+          <t>2962669</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5742699</t>
+          <t>5737322</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5867204</t>
+          <t>5865901</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,54%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>60448</t>
+          <t>66625</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>47911</t>
+          <t>52234</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>75835</t>
+          <t>80557</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>53598</t>
+          <t>55202</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>43938</t>
+          <t>45397</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>63929</t>
+          <t>64493</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>114046</t>
+          <t>121827</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>98452</t>
+          <t>104993</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>130547</t>
+          <t>140091</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>22,06%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>250995</t>
+          <t>252220</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>235608</t>
+          <t>238288</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>263532</t>
+          <t>266611</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>74,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>83,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>236037</t>
+          <t>260859</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>225706</t>
+          <t>251568</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>245697</t>
+          <t>270664</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>487031</t>
+          <t>513079</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>470530</t>
+          <t>494815</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>502625</t>
+          <t>529913</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>83,46%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>78392</t>
+          <t>79850</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>63007</t>
+          <t>62786</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>96811</t>
+          <t>99234</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>77097</t>
+          <t>82827</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>64161</t>
+          <t>69148</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>90727</t>
+          <t>96639</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>155489</t>
+          <t>162677</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>134113</t>
+          <t>139197</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>177230</t>
+          <t>182001</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>16,95%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>438117</t>
+          <t>448887</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>419698</t>
+          <t>429503</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>453502</t>
+          <t>465951</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>436628</t>
+          <t>462386</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>422998</t>
+          <t>448574</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>449564</t>
+          <t>476065</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>874745</t>
+          <t>911274</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>853004</t>
+          <t>891950</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>896121</t>
+          <t>934754</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>87,04%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>516509</t>
+          <t>528737</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>516509</t>
+          <t>528737</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>516509</t>
+          <t>528737</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>513725</t>
+          <t>545213</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>513725</t>
+          <t>545213</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>513725</t>
+          <t>545213</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1030234</t>
+          <t>1073951</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1030234</t>
+          <t>1073951</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1030234</t>
+          <t>1073951</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>68711</t>
+          <t>67838</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>57025</t>
+          <t>56914</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>81463</t>
+          <t>81497</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>83770</t>
+          <t>84918</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>71935</t>
+          <t>72637</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>97417</t>
+          <t>97682</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>152481</t>
+          <t>152756</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>134185</t>
+          <t>135922</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>170901</t>
+          <t>170776</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,4%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>247339</t>
+          <t>248155</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>234587</t>
+          <t>234496</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>259025</t>
+          <t>259079</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>74,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>265358</t>
+          <t>271463</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>251711</t>
+          <t>258699</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>277193</t>
+          <t>283744</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>512697</t>
+          <t>519619</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>494277</t>
+          <t>501599</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>530993</t>
+          <t>536453</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>79,78%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>62210</t>
+          <t>69025</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49783</t>
+          <t>54648</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>78782</t>
+          <t>86817</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>82961</t>
+          <t>89778</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51490</t>
+          <t>77013</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>108234</t>
+          <t>103921</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>145171</t>
+          <t>158803</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>104351</t>
+          <t>139543</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>172297</t>
+          <t>180346</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>22,68%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>250347</t>
+          <t>304120</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>233775</t>
+          <t>286328</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>262774</t>
+          <t>318497</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>392757</t>
+          <t>332183</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>367484</t>
+          <t>318040</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>424228</t>
+          <t>344948</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>75,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>643103</t>
+          <t>636304</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>615977</t>
+          <t>614761</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>683923</t>
+          <t>655564</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>82,45%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>34166</t>
+          <t>36407</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26688</t>
+          <t>28323</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43513</t>
+          <t>45209</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>55302</t>
+          <t>57351</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>47063</t>
+          <t>49476</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>64378</t>
+          <t>65697</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>89468</t>
+          <t>93757</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>78454</t>
+          <t>81666</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>101160</t>
+          <t>106182</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>24,53%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>144576</t>
+          <t>169258</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>135229</t>
+          <t>160456</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>152054</t>
+          <t>177342</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>153354</t>
+          <t>169864</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>144278</t>
+          <t>161518</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>161593</t>
+          <t>177739</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>71,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>297930</t>
+          <t>339122</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>286238</t>
+          <t>326697</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>308944</t>
+          <t>351213</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>81,13%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>73811</t>
+          <t>72786</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>62377</t>
+          <t>61899</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>86420</t>
+          <t>85713</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,27 +12447,27 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>60405</t>
+          <t>62430</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>51598</t>
+          <t>52878</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>70633</t>
+          <t>72490</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>134216</t>
+          <t>135217</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>119026</t>
+          <t>120843</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>148919</t>
+          <t>151483</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,34%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>195825</t>
+          <t>197921</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>183216</t>
+          <t>184994</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>207259</t>
+          <t>208808</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>72,63%</t>
+          <t>73,11%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>77,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,22 +12560,22 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>196651</t>
+          <t>201320</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>186423</t>
+          <t>191260</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>205458</t>
+          <t>210872</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -12585,7 +12585,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>392476</t>
+          <t>399240</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>377773</t>
+          <t>382974</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>407666</t>
+          <t>413614</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>77,39%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>110350</t>
+          <t>130503</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>91634</t>
+          <t>111194</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>129153</t>
+          <t>155126</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>330471</t>
+          <t>157926</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>157596</t>
+          <t>139496</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>587135</t>
+          <t>177059</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>440820</t>
+          <t>288429</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>264543</t>
+          <t>260481</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>801865</t>
+          <t>316812</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>21,24%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>513929</t>
+          <t>589184</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>495126</t>
+          <t>564561</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>532645</t>
+          <t>608493</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>518794</t>
+          <t>614131</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>262130</t>
+          <t>594998</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>691669</t>
+          <t>632561</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1032724</t>
+          <t>1203315</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>671679</t>
+          <t>1174932</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1209001</t>
+          <t>1231263</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>82,54%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>125251</t>
+          <t>140046</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>56136</t>
+          <t>121074</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>177018</t>
+          <t>160436</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>159037</t>
+          <t>175791</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>142612</t>
+          <t>157287</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>179945</t>
+          <t>196858</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>284288</t>
+          <t>315837</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>169733</t>
+          <t>290804</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>343874</t>
+          <t>345789</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,24%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>803469</t>
+          <t>658026</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>751702</t>
+          <t>637636</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>872584</t>
+          <t>676998</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>555814</t>
+          <t>654215</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>534906</t>
+          <t>633148</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>572239</t>
+          <t>672719</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1359284</t>
+          <t>1312241</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1299698</t>
+          <t>1282289</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1473839</t>
+          <t>1337274</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>82,14%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>714851</t>
+          <t>830006</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>714851</t>
+          <t>830006</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>714851</t>
+          <t>830006</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1643572</t>
+          <t>1628078</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1643572</t>
+          <t>1628078</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1643572</t>
+          <t>1628078</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>613339</t>
+          <t>663080</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>468711</t>
+          <t>618741</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>672069</t>
+          <t>705213</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>902641</t>
+          <t>766222</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>721775</t>
+          <t>726964</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1386413</t>
+          <t>803573</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1515979</t>
+          <t>1429302</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1305539</t>
+          <t>1369921</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2162816</t>
+          <t>1483872</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>20,43%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2844598</t>
+          <t>2867772</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2785868</t>
+          <t>2825639</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2989226</t>
+          <t>2912111</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2755392</t>
+          <t>2966423</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2271620</t>
+          <t>2929072</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2936258</t>
+          <t>3005681</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>5599990</t>
+          <t>5834195</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4953153</t>
+          <t>5779625</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5810430</t>
+          <t>5893576</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,14%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3457937</t>
+          <t>3530852</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3457937</t>
+          <t>3530852</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3457937</t>
+          <t>3530852</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3658033</t>
+          <t>3732645</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3658033</t>
+          <t>3732645</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3658033</t>
+          <t>3732645</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7115969</t>
+          <t>7263497</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7115969</t>
+          <t>7263497</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7115969</t>
+          <t>7263497</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
